--- a/entity_plans/130 COMMUNICATIONS AUTHORITY OF KENYA.xlsx
+++ b/entity_plans/130 COMMUNICATIONS AUTHORITY OF KENYA.xlsx
@@ -8,6 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="Procurement Plan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="4" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="5" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="6" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="8" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="9" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="10" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="11" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="12" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="13" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="14" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="16" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="17" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="18" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="19" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="20" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="21" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="23" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="24" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="25" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="26" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="27" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +41,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;KES&quot; #,##0.00"/>
+  </numFmts>
   <fonts count="4">
     <font>
       <name val="Calibri"/>
@@ -97,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -122,6 +149,12 @@
     </xf>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -488,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -504,7 +537,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>COMMUNICATIONS AUTHORITY OF KENYA (COMMA/1039/APP/2026-27/3) TOTAL COST</t>
+          <t>COMMUNICATIONS AUTHORITY OF KENYA (COMMA/1039/APP/2026-27/4) TOTAL COST</t>
         </is>
       </c>
     </row>
@@ -556,11 +589,11 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Editorial &amp; Design &amp; Graphic &amp; Fine Art Services</t>
+          <t>Public Utilities &amp; Public Sector Related Services</t>
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>5000000</v>
+        <v>55717000</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -569,22 +602,22 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>OPEN/RFQ</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -594,20 +627,20 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Travel &amp; Food &amp; Lodging &amp; Entertainment Services</t>
+          <t>Industrial Production &amp; Manufacturing Services</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>2000000</v>
+        <v>4400000</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -632,25 +665,25 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Management &amp; Business Professionals &amp; Administrative Services</t>
+          <t>Building &amp; Construction &amp; Maintenance Services</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>93500000</v>
+        <v>23780000</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>OPEN/RFQ AGPO</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>OPEN/RFQ WOMEN</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -670,25 +703,25 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Building &amp; Construction &amp; Maintenance Services</t>
+          <t>Distribution &amp; Conditioning Systems &amp; Equipment &amp; Components</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>23780000</v>
+        <v>10000000</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>OPEN/RFQ AGPO</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>OPEN/RFQ WOMEN</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -708,20 +741,20 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Mining &amp; Oil &amp; Gas Services</t>
+          <t>Furniture &amp; Furnishings</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>5000000</v>
+        <v>12000000</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -746,11 +779,11 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Land and Buildings and Structures and Thoroughfares</t>
+          <t>Transportation &amp; Storage &amp; Mail Services</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>260000000</v>
+        <v>1000000</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
@@ -759,12 +792,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -784,11 +817,11 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Engineering &amp; Research &amp; Technology Based Services</t>
+          <t>Food, Beverage &amp; Tobacco Products</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>344012000</v>
+        <v>18100000</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
@@ -802,12 +835,12 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -822,11 +855,11 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Education &amp; Training Services</t>
+          <t>National Defense &amp; Public Order &amp; Security &amp; Safety Services</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>10000000</v>
+        <v>36738000</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -835,12 +868,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -860,11 +893,11 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Laboratory &amp; Measuring &amp; Observing &amp; Testing Equipment</t>
+          <t>Industrial Cleaning Services</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>9000000</v>
+        <v>5404000</v>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
@@ -873,12 +906,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -898,25 +931,25 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Manufacturing Components &amp; Supplies</t>
+          <t xml:space="preserve"> Financial Instruments, Products, Contracts and Agreements</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>2066100</v>
+        <v>36000000</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>OPEN/RFQ AGPO</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>OPEN/RFQ YOUTH</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -936,30 +969,30 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Defense &amp; Law Enforcement &amp; Security &amp; Safety Equipment &amp; Supplies</t>
+          <t>Engineering &amp; Research &amp; Technology Based Services</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1409997</v>
+        <v>344012000</v>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>RFQ AGPO</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>RFQ YOUTH</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -992,7 +1025,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>OPEN/RFQ YOUTH</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1012,11 +1045,11 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Tools &amp; General Machinery</t>
+          <t>Electrical systems &amp; Lighting &amp; components &amp; accessories &amp; supplies</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>2280000</v>
+        <v>18800000</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
@@ -1025,7 +1058,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>RFQ YOUTH</t>
+          <t>RFQ/RFQ YOUTH</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1050,11 +1083,11 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Industrial Production &amp; Manufacturing Services</t>
+          <t>Management &amp; Business Professionals &amp; Administrative Services</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>4400000</v>
+        <v>93500000</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
@@ -1088,15 +1121,15 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Transportation &amp; Storage &amp; Mail Services</t>
+          <t>Mining &amp; Oil &amp; Gas Services</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1000000</v>
+        <v>5000000</v>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1106,7 +1139,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1126,11 +1159,11 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco Products</t>
+          <t>Land and Buildings and Structures and Thoroughfares</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>18100000</v>
+        <v>260000000</v>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
@@ -1139,7 +1172,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -1164,11 +1197,11 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>National Defense &amp; Public Order &amp; Security &amp; Safety Services</t>
+          <t>Education &amp; Training Services</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>36738000</v>
+        <v>10000000</v>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
@@ -1202,11 +1235,11 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Industrial Cleaning Services</t>
+          <t>Laboratory &amp; Measuring &amp; Observing &amp; Testing Equipment</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>5404000</v>
+        <v>9000000</v>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
@@ -1240,15 +1273,15 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Financial Instruments, Products, Contracts and Agreements</t>
+          <t>Manufacturing Components &amp; Supplies</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>36000000</v>
+        <v>2066100</v>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>OPEN/RFQ AGPO</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1258,7 +1291,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>OPEN/RFQ YOUTH</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1278,15 +1311,15 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Financial &amp; Insurance Services</t>
+          <t>Defense &amp; Law Enforcement &amp; Security &amp; Safety Equipment &amp; Supplies</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>30000000</v>
+        <v>1409997</v>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RFQ AGPO</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1296,7 +1329,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RFQ YOUTH</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -1316,25 +1349,25 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Public Utilities &amp; Public Sector Related Services</t>
+          <t>Tools &amp; General Machinery</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>55717000</v>
+        <v>2280000</v>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>RFQ AGPO</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>RFQ YOUTH</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>OPEN/RFQ</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1354,15 +1387,15 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Paper Materials &amp; Products</t>
+          <t>Financial &amp; Insurance Services</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>4464500</v>
+        <v>30000000</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1372,12 +1405,12 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>OPEN/RFQ</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>OPEN/RFQ</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -1392,11 +1425,11 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Office Equipment &amp; Accessories &amp; Supplies</t>
+          <t>Paper Materials &amp; Products</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>4734700</v>
+        <v>4464500</v>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
@@ -1430,11 +1463,11 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Musical Instruments &amp; Games &amp; Toys &amp; Arts &amp; Crafts &amp; Educational Equipment &amp; Materials &amp; Accessories &amp; Supplies</t>
+          <t>Office Equipment &amp; Accessories &amp; Supplies</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>675000</v>
+        <v>4734700</v>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
@@ -1448,12 +1481,12 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>OPEN/RFQ</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>OPEN/RFQ</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -1468,11 +1501,11 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Published Products</t>
+          <t>Musical Instruments &amp; Games &amp; Toys &amp; Arts &amp; Crafts &amp; Educational Equipment &amp; Materials &amp; Accessories &amp; Supplies</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>1000000</v>
+        <v>675000</v>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
@@ -1506,15 +1539,15 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Electrical systems &amp; Lighting &amp; components &amp; accessories &amp; supplies</t>
+          <t>Published Products</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>18800000</v>
+        <v>1000000</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>RFQ AGPO</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -1524,7 +1557,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>RFQ/RFQ YOUTH</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -1539,21 +1572,97 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="A29" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Editorial &amp; Design &amp; Graphic &amp; Fine Art Services</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Travel &amp; Food &amp; Lodging &amp; Entertainment Services</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="8">
-        <f>SUM(C3:C28)</f>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="8">
+        <f>SUM(C3:C30)</f>
         <v/>
       </c>
-      <c r="D29" s="7" t="n"/>
-      <c r="E29" s="7" t="n"/>
-      <c r="F29" s="7" t="n"/>
-      <c r="G29" s="7" t="n"/>
-      <c r="H29" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="7" t="n"/>
+      <c r="G31" s="7" t="n"/>
+      <c r="H31" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1561,4 +1670,5915 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Industrial Cleaning Services — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>7611150101</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>BUILDING CLEANING SERVICES</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>5404000</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>5404000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Financial Instruments, Products, Contracts and Agreements — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>64122003</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Group life insurance policy</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>36000000</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>36000000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr"/>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="61" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Engineering &amp; Research &amp; Technology Based Services — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>81111504</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Application programming services</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>225000000</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>225000000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr"/>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>81112501</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Computer software licensing service</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>54000000</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>54000000</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr"/>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>81112501</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Computer software licensing service</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>14700000</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>14700000</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr"/>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>8111210101</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>INTERNET SERVICE PROVIDERS ISP</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>13148000</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>13148000</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>81111504</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Application programming services</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>81112501</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Computer software licensing service</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr"/>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>81112501</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Computer software licensing service</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>8834000</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>8834000</v>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>81111819</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Quality assurance services</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr"/>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>81112306</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Printer, scanner and multifunctional equipment maintenance</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>2150000</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>2150000</v>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>81112501</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Computer software licensing service</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>1680000</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>1680000</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr"/>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Information Technology Broadcasting &amp; Telecommunications — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>4321150301</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>FIELD MOBILE TOUGH NOTEBOOK COMPUTER</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>85.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>400000</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>34000000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>43211521</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>All in one desktop computer</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>300.00</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>70880</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>21264000</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>4321150901</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>TABLET COMPUTERS</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>400000</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>4323320501</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>VIRUS PROTECTION SOFTWARE OR FIREWALL</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>15200000</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>15200000</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>43233415</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Backup or archival software</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>43211521</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>All in one desktop computer</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>200000</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>43212110</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Multi function printers</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>2150000</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>6450000</v>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>4319150102</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>SMART PHONES</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>160000</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>6400000</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>4319150102</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>SMART PHONES</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>100000</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>4319150102</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>SMART PHONES</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>200000</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>4319150102</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>SMART PHONES</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>250000</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>4319150102</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>SMART PHONES</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>80000</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>43233508</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Mobile operator specific application software</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>4319150102</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>SMART PHONES</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>60000</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>660000</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>4323320501</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>VIRUS PROTECTION SOFTWARE OR FIREWALL</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>500000</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Electrical systems &amp; Lighting &amp; components &amp; accessories &amp; supplies — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>39121011</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Uninterruptible power supply UPS</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>181.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>9050000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>39121011</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Uninterruptible power supply UPS</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>270000</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>6750000</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr"/>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>39121011</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Uninterruptible power supply UPS</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Management &amp; Business Professionals &amp; Administrative Services — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>80101514</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Business regulatory and compliance research service</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>87000000</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>87000000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr"/>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>80171501</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Polling and survey and public opinion monitoring and analysis</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Land and Buildings and Structures and Thoroughfares — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>95121806</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Mobile telephone base station</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Works</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>225000000</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>225000000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr"/>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>95141803</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Container unit</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>35000000</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Education &amp; Training Services — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>8614170301</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>COMPUTER / DIGITAL EQUIPMENT TRAINING SERVICES</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Laboratory &amp; Measuring &amp; Observing &amp; Testing Equipment — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>41113716</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Fiber optic fault locators</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>450000</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>41115316</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Reflectometers</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>450000</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Manufacturing Components &amp; Supplies — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>31242105</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Optical fiber identifiers</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>200000</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Public Utilities &amp; Public Sector Related Services — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>8311160101</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>MOBILE COMMUNICATIONS SERVICES OR AIRTIME</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>54200000</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>54200000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr"/>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>8311160301</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>CELLULAR TELEPHONE SERVICES</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>1517000</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>1517000</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr"/>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Defense &amp; Law Enforcement &amp; Security &amp; Safety Equipment &amp; Supplies — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>4618153103</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>JACKETS FIRST AIDER REFLECTIVE</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>17.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>27647</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>469999</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>46181602</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Hazardous material protective footwear</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>17.00</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>27647</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>469999</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>4618170401</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>HELMETS FIREFIGHTING</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>17.00</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>27647</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>469999</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tools &amp; General Machinery — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>27113203</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Computer tool kits</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>2280000</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>2280000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Paper Materials &amp; Products — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>14111501</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Onion skin paper</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>8500</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr"/>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>1411150708</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>PAPERS PRINTING A4 80GSM</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>1500.00</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>750</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>1125000</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr"/>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>14111501</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Onion skin paper</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>8500</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>850000</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr"/>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>1411151103</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>PADS RULED A4</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>1000.00</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>270</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>270000</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>1411151413</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>NOTEBOOKS FIELD</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>1000.00</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>225</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>225000</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Office Equipment &amp; Accessories &amp; Supplies — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>4412150604</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>ENVELOPES MANILA A4</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>20000.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>4412150605</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>ENVELOPES MANILA A5</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>20000.00</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>4412150603</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>ENVELOPES MANILA A3</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>5000.00</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>450000</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr"/>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>44122036</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Box file</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>1000.00</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>450</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>450000</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr"/>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Musical Instruments &amp; Games &amp; Toys &amp; Arts &amp; Crafts &amp; Educational Equipment &amp; Materials &amp; Accessories &amp; Supplies — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>60121157</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Embossed card</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>4500</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>675000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Published Products — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>5510150901</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>EDUCATIONAL OR VOCATIONAL TEXTBOOKS</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr"/>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Editorial &amp; Design &amp; Graphic &amp; Fine Art Services — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>8210180101</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>ADVERTISING CAMPAIGN SERVICES</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr"/>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Industrial Production &amp; Manufacturing Services — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>73152121</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Machine maintenance and alignment services</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>73152108</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Electrical equipment maintenance and repair service</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="69" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Building &amp; Construction &amp; Maintenance Services — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>72103302</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Telecom equipment maintenance or support</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>7300000</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>7300000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr"/>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>72103302</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Telecom equipment maintenance or support</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>6400000</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>6400000</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr"/>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>72102902</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Landscaping services</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>72101509</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Fire protection system and equipment maintenance or repair service</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>3180000</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>3180000</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr"/>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>72103302</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Telecom equipment maintenance or support</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Distribution &amp; Conditioning Systems &amp; Equipment &amp; Components — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>40101701</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Air conditioners</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Works</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Furniture &amp; Furnishings — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>56101532</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Furniture set</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Works</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Transportation &amp; Storage &amp; Mail Services — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>7811180401</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>TAXICAB SERVICES</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr"/>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Food, Beverage &amp; Tobacco Products — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>5020231003</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>BOTTLED WATER 18.9 LTR</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>18100000</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>18100000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>National Defense &amp; Public Order &amp; Security &amp; Safety Services — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>9212150402</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>SECURITY GUARD SERVICES</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>28380000</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>28380000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>9212150402</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>SECURITY GUARD SERVICES</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>8358000</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>8358000</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr"/>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>